--- a/data/trans_camb/IMC_inf_R3-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R3-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-9.867549269783662</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-9.325728147666343</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-6.695782029921676</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-8.088669753599401</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-8.241143131608245</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-8.50384516481898</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-16.69052047495155</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-20.15821500044943</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-14.1968038473167</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-16.11009095935623</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-13.02413416666759</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-14.99660071197556</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-2.347284564013754</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.8812206457192195</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.6017524264659035</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.955920197301716</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-3.499344892445285</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-0.3203101299115348</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.2986673611208105</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.2822677181782783</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.3058337011849071</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.3694546503083602</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2989699920196499</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3085002262988393</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.4529012789823947</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5528710121422998</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.5399392612164275</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.6432527534011468</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.436297318302471</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5087169812880356</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>-0.08006639873876732</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.03924238651755248</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-0.02983332834978121</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.1154813901178792</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.1424114463997532</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.000646613767723339</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.4253993533629818</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.9317014527285</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.28024455639602</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-6.705972245175349</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.819267424435381</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-5.210045272034527</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-7.529504794967755</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.1507913952001</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-10.18969229492143</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-13.26380703341457</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-6.890766835205316</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-9.894620363587928</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>6.393067898875832</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.387411900536754</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.034961471201879</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.720277316486487</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.961095151173247</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.4663687735039935</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.02123632702979843</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.1962741531542293</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.1771894845534616</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3622375542809945</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.09430451436235507</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2700706793216986</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.3271681733792073</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.4775662083016083</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.4675013821715032</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.6016779891422193</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3094330508822407</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.457439303525889</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.3953718435851235</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.2768866829720755</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.2874890072872252</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.08011696313401549</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1746460720675226</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.04508731190853195</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-1.622641616546572</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.705836960569016</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.222070625502716</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-6.270840741551654</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-1.43157976824157</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-4.270112488640418</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-9.989098172054719</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-10.49019964502938</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-9.732697406944975</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-14.36941753401172</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-7.068669867779182</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-9.116081893181914</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>7.1494265006605</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.736918752377444</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.09169039516878</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.3504866824978221</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.92720824060674</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.399135271390214</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.08446504047768529</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.140849726809604</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.06638636024487216</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.3406499459355051</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.07606756715753143</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2268941456883302</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.4223285407957602</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.4288855073059376</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.4265801951540727</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.6018095424492403</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.3308008531193439</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.4243249713504966</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.4943360726341036</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.3384780920272005</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.4543874808239091</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.02974841417670293</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2602569356372432</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.08341793715497098</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-7.375899302533726</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-12.99786130638801</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-6.467934195158728</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-10.4900084714004</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-6.586476085047732</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-12.09227400844524</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-20.83580029609017</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-23.48100083370586</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-18.44620302549132</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-20.87804974497152</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-14.89544806855871</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-20.20320500854483</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>3.519914347485898</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-2.85396653877132</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.63049779820302</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-2.668447818174894</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.47935785590999</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-4.711464553791227</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.2609788238285617</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.4598987075193202</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.3687530880183049</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.5980615912979532</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2833928214827153</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.5202878755112895</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.5653434751961189</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.6666862491077959</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.7578034885249008</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.8046489230153689</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.5295097830240171</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.6759699985594034</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.1801876719514979</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-0.1290202704622166</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.3825517280476532</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.1790695486579538</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.0996718608012286</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.2512790553325808</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-4.59357660692141</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-8.176894577260633</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-4.309602406798632</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-8.483367974778536</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-4.429029124594256</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-8.224474515612457</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-8.667173467137159</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-12.2922566502962</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-8.123753241174633</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-12.19146592458246</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-7.660393407744643</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-11.04049076266375</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-0.318419718897971</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-4.006226967776063</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-0.5517462858199403</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-4.969488994366809</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-1.558399708296019</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-5.415452077274625</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.1817856483044139</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.3235914427995958</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.2205674490654702</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.4341827057476945</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1969989747923561</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.3658167517536797</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.3170732134117861</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.4489938535962267</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.377177414000966</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.5571461327943579</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3154330571710233</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.4599251717074972</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.01137122533902784</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.16530744262365</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.03109637785144761</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.275511814296007</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.07850506011976968</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.252246501195185</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
